--- a/Cronograma(2ºSemestre).xlsx
+++ b/Cronograma(2ºSemestre).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2026\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2026\Desktop\Patinhas Felizes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45A9D593-8C9E-4AE1-9B68-937FFA1CD28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F3D9DD-F6C8-48DB-8A90-0DF62698F83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{08C7B1D9-FAF1-4333-ABBB-F5A2186B84FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>ATIVIDADES</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>Definição do objetivo do website</t>
+  </si>
+  <si>
+    <t>Mínimo:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máximo: </t>
   </si>
 </sst>
 </file>
@@ -167,11 +173,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -189,6 +192,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F214DF-C21D-4A8B-8694-9ACBEE2BE205}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.5546875" customWidth="1"/>
@@ -534,333 +547,351 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="4">
-        <v>46239</v>
-      </c>
-      <c r="C3" s="5">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
-        <v>46239</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="B3" s="3">
+        <v>46239</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>46239</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="4">
-        <v>46239</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>46239</v>
-      </c>
-      <c r="E4" s="6">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="B4" s="3">
+        <v>46239</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46239</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="4">
-        <v>46239</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4">
-        <v>46239</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="B5" s="3">
+        <v>46239</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46239</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="4">
-        <v>46239</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
-        <v>46239</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="B6" s="3">
+        <v>46239</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46239</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>46244</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>46246</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>0</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="8">
-        <v>46239</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>46239</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="B8" s="7">
+        <v>46239</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7">
+        <v>46239</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="8">
-        <v>46239</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>46239</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="B9" s="7">
+        <v>46239</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7">
+        <v>46239</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>46244</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>2</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>46246</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>0</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>46251</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>29</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>46281</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>0</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>46251</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>29</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
+        <v>46351</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7">
+        <v>46251</v>
+      </c>
+      <c r="C13" s="4">
+        <v>29</v>
+      </c>
+      <c r="D13" s="7">
         <v>46281</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E13" s="5">
         <v>0</v>
       </c>
-      <c r="F12" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="8">
-        <v>46251</v>
-      </c>
-      <c r="C13" s="5">
-        <v>29</v>
-      </c>
-      <c r="D13" s="8">
-        <v>46281</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7">
+        <v>46286</v>
+      </c>
+      <c r="C14" s="4">
+        <v>35</v>
+      </c>
+      <c r="D14" s="7">
+        <v>46321</v>
+      </c>
+      <c r="E14" s="5">
         <v>0</v>
       </c>
-      <c r="F13" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="8">
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7">
         <v>46286</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C15" s="4">
         <v>35</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D15" s="7">
         <v>46321</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E15" s="5">
         <v>0</v>
       </c>
-      <c r="F14" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="8">
-        <v>46286</v>
-      </c>
-      <c r="C15" s="5">
-        <v>35</v>
-      </c>
-      <c r="D15" s="8">
-        <v>46321</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46323</v>
+      </c>
+      <c r="C16" s="4">
+        <v>36</v>
+      </c>
+      <c r="D16" s="7">
+        <v>46358</v>
+      </c>
+      <c r="E16" s="5">
         <v>0</v>
       </c>
-      <c r="F15" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="8">
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7">
         <v>46323</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C17" s="4">
         <v>36</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D17" s="7">
         <v>46358</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E17" s="5">
         <v>0</v>
       </c>
-      <c r="F16" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="8">
-        <v>46323</v>
-      </c>
-      <c r="C17" s="5">
-        <v>36</v>
-      </c>
-      <c r="D17" s="8">
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="10">
+        <f>MIN(D3:D17)</f>
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="10">
+        <f>MAX(D3:D17)</f>
         <v>46358</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Cronograma(2ºSemestre).xlsx
+++ b/Cronograma(2ºSemestre).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2026\Desktop\Patinhas Felizes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F3D9DD-F6C8-48DB-8A90-0DF62698F83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096BD463-835C-4629-801C-310F3C767081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{08C7B1D9-FAF1-4333-ABBB-F5A2186B84FB}"/>
   </bookViews>
@@ -217,6 +217,1126 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Cronograma</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.40533232259011104"/>
+          <c:y val="0.16786448584598943"/>
+          <c:w val="0.52830129929410996"/>
+          <c:h val="0.79870187991796915"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>INÍCIO</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$A$3:$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>Escolher o setor para o qual criaremos o website</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Criação do nome do website</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Definição do objetivo do website</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Dividir páginas(Home, Serviços, Galeria e Contato)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Escopo</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Requisitos funcionais e não funcionais </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cronograma</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Introdução da documentação</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Wireframe de alta fidelidade</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Front-end </c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Metodologia da documentação</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Estruturação/normalização banco de dados</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Desenvolvimento da metodologia</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Projeto final</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Documentação final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$B$3:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46323</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46323</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1A80-407E-A100-B4A3D3F57DB1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TOTAL DE DIAS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$A$3:$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>Escolher o setor para o qual criaremos o website</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Criação do nome do website</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Definição do objetivo do website</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Dividir páginas(Home, Serviços, Galeria e Contato)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Escopo</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Requisitos funcionais e não funcionais </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cronograma</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Introdução da documentação</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Wireframe de alta fidelidade</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Front-end </c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Metodologia da documentação</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Estruturação/normalização banco de dados</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Desenvolvimento da metodologia</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Projeto final</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Documentação final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$C$3:$C$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>36</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1A80-407E-A100-B4A3D3F57DB1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="936732608"/>
+        <c:axId val="936731168"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="936732608"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="936731168"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="936731168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46358"/>
+          <c:min val="46239"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="936732608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9DC741D-4AA0-3F42-F575-08CABD86C7EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -899,5 +2019,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>